--- a/checklist_forms/037_daily_team_huddle_checklist--checklist_forms.xlsx
+++ b/checklist_forms/037_daily_team_huddle_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'attended',_'value':_'attended'}</t>
+          <t>attended</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Attended', 'value': 'Attended'}</t>
+          <t>Attended</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'absent',_'value':_'absent'}</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Absent', 'value': 'Absent'}</t>
+          <t>Absent</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'late',_'value':_'late'}</t>
+          <t>late</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Late', 'value': 'Late'}</t>
+          <t>Late</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'on_vacation',_'value':_'on_vacation'}</t>
+          <t>on_vacation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'On Vacation', 'value': 'On Vacation'}</t>
+          <t>On Vacation</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'working_remotely',_'value':_'working_remotely'}</t>
+          <t>working_remotely</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Working Remotely', 'value': 'Working Remotely'}</t>
+          <t>Working Remotely</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'technical_blocker',_'value':_'technical_blocker'}</t>
+          <t>technical_blocker</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Technical Blocker', 'value': 'Technical Blocker'}</t>
+          <t>Technical Blocker</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'non-technical_blocker',_'value':_'non-technical_blocker'}</t>
+          <t>non-technical_blocker</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Non-Technical Blocker', 'value': 'Non-Technical Blocker'}</t>
+          <t>Non-Technical Blocker</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'user_1',_'value':_'user_1'}</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'User 1', 'value': 'User 1'}</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'user_2',_'value':_'user_2'}</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'User 2', 'value': 'User 2'}</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'user_3',_'value':_'user_3'}</t>
+          <t>user_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'User 3', 'value': 'User 3'}</t>
+          <t>User 3</t>
         </is>
       </c>
     </row>
